--- a/grupos/1EV - Estadisticos 20211.xlsx
+++ b/grupos/1EV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -152,18 +152,18 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Bautista Sarao Eutiquio</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
-    <t>Bautista Sarao Eutiquio</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -182,139 +182,139 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>DAVID OSWALDO</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>JOSIAH</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>MIXCOHA</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RIVADENEYRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>JOSE RUBEN</t>
   </si>
   <si>
     <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>JOSIAH</t>
-  </si>
-  <si>
-    <t>OLIVER ULISES</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
   </si>
   <si>
     <t>MILKA SARAY</t>
@@ -848,13 +848,13 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -928,10 +928,10 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -996,19 +996,19 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1032,13 +1032,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
+        <v>9</v>
+      </c>
+      <c r="U6">
+        <v>9</v>
+      </c>
+      <c r="V6">
         <v>8</v>
-      </c>
-      <c r="U6">
-        <v>8</v>
-      </c>
-      <c r="V6">
-        <v>6</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1073,19 +1073,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1141,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1150,19 +1150,19 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1227,19 +1227,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1263,7 +1263,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1272,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1292,7 +1292,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1310,13 +1310,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1346,10 +1346,10 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1381,19 +1381,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1423,10 +1423,10 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1458,19 +1458,19 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1497,10 +1497,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1526,7 +1526,7 @@
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>-1</v>
@@ -1544,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1580,7 +1580,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>-1</v>
@@ -1612,19 +1612,19 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1651,13 +1651,13 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1689,19 +1689,19 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1775,7 +1775,7 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1811,7 +1811,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -1843,19 +1843,19 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1885,7 +1885,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F18">
         <v>-1</v>
@@ -1929,7 +1929,7 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -1965,7 +1965,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -1991,13 +1991,13 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>-1</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2006,10 +2006,10 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2042,10 +2042,10 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2065,7 +2065,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>7</v>
@@ -2083,10 +2083,10 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2151,19 +2151,19 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2193,10 +2193,10 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>10</v>
@@ -2228,19 +2228,19 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2270,10 +2270,10 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2293,10 +2293,10 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2311,13 +2311,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2347,10 +2347,10 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2364,37 +2364,37 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2418,19 +2418,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2498,25 +2498,25 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2530,30 +2530,30 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="G3">
         <v>4.76</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2562,30 +2562,30 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.9</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2594,30 +2594,30 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2626,30 +2626,30 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>28.57</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2658,25 +2658,25 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2686,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2721,10 +2721,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -2741,10 +2741,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -2761,10 +2761,10 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2781,10 +2781,10 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -2795,22 +2795,22 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920139</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2818,59 +2818,59 @@
         <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920141</v>
+        <v>21330051920144</v>
       </c>
       <c r="B8" t="s">
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920141</v>
+        <v>21330051920144</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2878,19 +2878,19 @@
         <v>21330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2898,16 +2898,16 @@
         <v>21330051920144</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -2918,79 +2918,79 @@
         <v>21330051920144</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920144</v>
+        <v>21330051920384</v>
       </c>
       <c r="B13" t="s">
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920144</v>
+        <v>21330051920384</v>
       </c>
       <c r="B14" t="s">
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920144</v>
+        <v>21330051920384</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2998,16 +2998,16 @@
         <v>21330051920384</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>44</v>
@@ -3018,79 +3018,79 @@
         <v>21330051920384</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920384</v>
+        <v>21330051920395</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920384</v>
+        <v>21330051920395</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920384</v>
+        <v>21330051920395</v>
       </c>
       <c r="B20" t="s">
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3098,19 +3098,19 @@
         <v>21330051920395</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3118,53 +3118,53 @@
         <v>21330051920395</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920395</v>
+        <v>21330051920147</v>
       </c>
       <c r="B23" t="s">
         <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920395</v>
+        <v>21330051920147</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -3175,76 +3175,76 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920395</v>
+        <v>21330051920147</v>
       </c>
       <c r="B25" t="s">
         <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920395</v>
+        <v>21330051920148</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920147</v>
+        <v>21330051920148</v>
       </c>
       <c r="B27" t="s">
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920147</v>
+        <v>21330051920148</v>
       </c>
       <c r="B28" t="s">
         <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -3255,342 +3255,82 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920147</v>
+        <v>21330051920148</v>
       </c>
       <c r="B29" t="s">
         <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920148</v>
+        <v>21330051920382</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920148</v>
+        <v>21330051920392</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920148</v>
-      </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s">
-        <v>71</v>
-      </c>
-      <c r="D33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920148</v>
-      </c>
-      <c r="B34" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920148</v>
-      </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920382</v>
-      </c>
-      <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920382</v>
-      </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920382</v>
-      </c>
-      <c r="B38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920382</v>
-      </c>
-      <c r="B39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920392</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920392</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" t="s">
-        <v>72</v>
-      </c>
-      <c r="D41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920392</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920392</v>
-      </c>
-      <c r="B43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>83</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920392</v>
-      </c>
-      <c r="B44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" t="s">
-        <v>72</v>
-      </c>
-      <c r="D44" t="s">
-        <v>83</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920392</v>
-      </c>
-      <c r="B45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D45" t="s">
-        <v>83</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3629,118 +3369,118 @@
         <v>21330051920144</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920395</v>
+        <v>21330051920384</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920392</v>
+        <v>21330051920395</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920384</v>
+        <v>21330051920148</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
         <v>78</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920148</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920147</v>
+        <v>21330051920135</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920382</v>
+        <v>21330051920136</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3748,30 +3488,30 @@
         <v>21330051920141</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920135</v>
+        <v>21330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -3779,47 +3519,47 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920136</v>
+        <v>21330051920392</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920139</v>
+        <v>21330051920137</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920137</v>
+        <v>21330051920138</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -3830,13 +3570,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920138</v>
+        <v>21330051920139</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
@@ -3850,10 +3590,10 @@
         <v>21330051920140</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3867,10 +3607,10 @@
         <v>21330051920142</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3884,10 +3624,10 @@
         <v>21330051920143</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3901,10 +3641,10 @@
         <v>21330051920381</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3918,10 +3658,10 @@
         <v>21330051920145</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3935,10 +3675,10 @@
         <v>21330051920146</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3952,10 +3692,10 @@
         <v>21330051920149</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3969,10 +3709,10 @@
         <v>21330051920150</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>106</v>
@@ -3988,7 +3728,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4026,10 +3766,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4049,10 +3789,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -4072,10 +3812,10 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4095,10 +3835,10 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4112,24 +3852,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920139</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920141</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920392</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20211.xlsx
+++ b/grupos/1EV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -152,12 +152,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -203,142 +203,142 @@
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>DAVID OSWALDO</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>JOSIAH</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RIVADENEYRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>DAVID OSWALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>JOSIAH</t>
-  </si>
-  <si>
-    <t>OLIVER ULISES</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>JOSE RUBEN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN ALFONSO</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ASHLEY NALLELY</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ASHLEY NALLELY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1011,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1165,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1242,7 +1242,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1396,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1473,7 +1473,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1509,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1627,7 +1627,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1858,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2166,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2243,7 +2243,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2356,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2379,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2397,7 +2397,7 @@
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2433,7 +2433,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2553,7 +2553,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2562,30 +2562,30 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>76.19</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>33.33</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -2686,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2721,10 +2721,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -2741,10 +2741,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -2761,10 +2761,10 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -2781,10 +2781,10 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -2801,10 +2801,10 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -2821,10 +2821,10 @@
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -2841,16 +2841,16 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2861,10 +2861,10 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -2881,10 +2881,10 @@
         <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -2901,16 +2901,16 @@
         <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2921,10 +2921,10 @@
         <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -2941,16 +2941,16 @@
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2961,10 +2961,10 @@
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -2981,10 +2981,10 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
@@ -3001,16 +3001,16 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3021,10 +3021,10 @@
         <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -3041,16 +3041,16 @@
         <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3061,10 +3061,10 @@
         <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -3081,10 +3081,10 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -3101,16 +3101,16 @@
         <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3121,10 +3121,10 @@
         <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -3141,16 +3141,16 @@
         <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3161,10 +3161,10 @@
         <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -3181,16 +3181,16 @@
         <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3201,16 +3201,16 @@
         <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3221,10 +3221,10 @@
         <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -3241,10 +3241,10 @@
         <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -3261,16 +3261,16 @@
         <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3284,53 +3284,13 @@
         <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920382</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920392</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3372,10 +3332,10 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -3389,10 +3349,10 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3406,10 +3366,10 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -3423,10 +3383,10 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -3440,10 +3400,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3457,10 +3417,10 @@
         <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3474,10 +3434,10 @@
         <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -3491,10 +3451,10 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -3511,38 +3471,38 @@
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920392</v>
+        <v>21330051920137</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920137</v>
+        <v>21330051920138</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -3553,13 +3513,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920138</v>
+        <v>21330051920139</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -3570,13 +3530,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920139</v>
+        <v>21330051920140</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>98</v>
@@ -3587,13 +3547,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920140</v>
+        <v>21330051920142</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3604,13 +3564,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920142</v>
+        <v>21330051920143</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3621,13 +3581,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920143</v>
+        <v>21330051920381</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3638,13 +3598,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920381</v>
+        <v>21330051920145</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3655,13 +3615,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920145</v>
+        <v>21330051920146</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3672,13 +3632,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920146</v>
+        <v>21330051920149</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3689,13 +3649,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920149</v>
+        <v>21330051920150</v>
       </c>
       <c r="B21" t="s">
         <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3706,13 +3666,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920150</v>
+        <v>21330051920392</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
         <v>106</v>
@@ -3728,7 +3688,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3766,10 +3726,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3789,10 +3749,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -3812,10 +3772,10 @@
         <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3835,10 +3795,10 @@
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -3858,10 +3818,10 @@
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3881,10 +3841,10 @@
         <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3898,24 +3858,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920392</v>
+        <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920382</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20211.xlsx
+++ b/grupos/1EV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -146,10 +146,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
@@ -2059,7 +2059,7 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2498,30 +2498,30 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,22 +2533,22 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>61.9</v>
       </c>
       <c r="G3">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>33.33</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2686,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2730,7 +2730,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2750,7 +2750,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2770,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2790,7 +2790,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2810,7 +2810,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2830,7 +2830,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2870,7 +2870,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2890,7 +2890,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2970,7 +2970,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2990,7 +2990,7 @@
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3070,7 +3070,7 @@
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3090,7 +3090,7 @@
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3170,7 +3170,7 @@
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3230,7 +3230,7 @@
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3247,50 +3247,30 @@
         <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920148</v>
+        <v>21330051920382</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920382</v>
-      </c>
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3377,33 +3357,33 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920148</v>
+        <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920147</v>
+        <v>21330051920148</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -3735,7 +3715,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -3758,7 +3738,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -3781,7 +3761,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -3804,7 +3784,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -3827,7 +3807,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -3850,7 +3830,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -3873,7 +3853,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3896,7 +3876,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9">
         <v>-1</v>

--- a/grupos/1EV - Estadisticos 20211.xlsx
+++ b/grupos/1EV - Estadisticos 20211.xlsx
@@ -2154,7 +2154,7 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2190,7 +2190,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>8</v>

--- a/grupos/1EV - Estadisticos 20211.xlsx
+++ b/grupos/1EV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="107">
   <si>
     <t>Materia</t>
   </si>
@@ -146,24 +146,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -182,15 +182,39 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PEÑA</t>
   </si>
   <si>
@@ -203,21 +227,45 @@
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>RIVADENEYRA</t>
   </si>
   <si>
@@ -227,21 +275,51 @@
     <t>GALICIA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEDRO ANGEL</t>
   </si>
   <si>
     <t>DAVID OSWALDO</t>
   </si>
   <si>
+    <t>GAEL JARED</t>
+  </si>
+  <si>
+    <t>JOSE RUBEN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN ALFONSO</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
     <t>ALBERTO SHAKIB</t>
   </si>
   <si>
+    <t>ASHLEY NALLELY</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>KARLA</t>
   </si>
   <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
     <t>JOSIAH</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>OLIVER ULISES</t>
   </si>
   <si>
@@ -251,91 +329,13 @@
     <t>ROGELIO</t>
   </si>
   <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAEL JARED</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ASHLEY NALLELY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>JOSELIN</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -824,10 +824,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -842,10 +842,10 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -857,31 +857,31 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -890,10 +890,10 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -901,10 +901,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>6</v>
@@ -919,13 +919,13 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>7</v>
@@ -934,31 +934,31 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -967,10 +967,10 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1014,28 +1014,28 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1091,25 +1091,25 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1168,25 +1168,25 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1245,22 +1245,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1286,10 +1286,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1304,10 +1304,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1319,31 +1319,31 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1352,10 +1352,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1399,28 +1399,28 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>6</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1476,22 +1476,22 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1517,76 +1517,76 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1630,22 +1630,22 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1654,7 +1654,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1692,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1707,22 +1707,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1731,16 +1731,16 @@
         <v>7</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1748,76 +1748,76 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E16">
         <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1861,22 +1861,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1902,76 +1902,76 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1982,10 +1982,10 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -1994,16 +1994,16 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>10</v>
@@ -2012,43 +2012,43 @@
         <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2056,13 +2056,13 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2071,16 +2071,16 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -2089,34 +2089,34 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2125,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2169,22 +2169,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2246,28 +2246,28 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>7</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2279,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2290,7 +2290,7 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -2305,10 +2305,10 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -2320,31 +2320,31 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2353,10 +2353,10 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2400,37 +2400,37 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>6</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2501,27 +2501,27 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>61.9</v>
       </c>
       <c r="G2">
-        <v>4.76</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2530,30 +2530,30 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>61.9</v>
+        <v>80.95</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>19.05</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2562,30 +2562,30 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2594,30 +2594,30 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2626,30 +2626,30 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2686,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2711,566 +2711,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920135</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920136</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920141</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920144</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920144</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920144</v>
-      </c>
-      <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920384</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920384</v>
-      </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920384</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920384</v>
-      </c>
-      <c r="B16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920384</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920395</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920395</v>
-      </c>
-      <c r="B19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920395</v>
-      </c>
-      <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920395</v>
-      </c>
-      <c r="B21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920395</v>
-      </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920147</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920147</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920147</v>
-      </c>
-      <c r="B25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920148</v>
-      </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920148</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920148</v>
-      </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920382</v>
-      </c>
-      <c r="B29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" t="s">
-        <v>77</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3306,166 +2746,166 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920144</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920384</v>
+        <v>21330051920136</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920395</v>
+        <v>21330051920137</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920147</v>
+        <v>21330051920138</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920148</v>
+        <v>21330051920139</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920136</v>
+        <v>21330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920141</v>
+        <v>21330051920142</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920382</v>
+        <v>21330051920143</v>
       </c>
       <c r="B10" t="s">
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920137</v>
+        <v>21330051920381</v>
       </c>
       <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
         <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>87</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -3476,13 +2916,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920138</v>
+        <v>21330051920144</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s">
         <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
@@ -3493,13 +2933,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920139</v>
+        <v>21330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -3510,10 +2950,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920140</v>
+        <v>21330051920384</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>80</v>
@@ -3527,13 +2967,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920142</v>
+        <v>21330051920146</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>99</v>
@@ -3544,13 +2984,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920143</v>
+        <v>21330051920395</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
         <v>100</v>
@@ -3561,13 +3001,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920381</v>
+        <v>21330051920147</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -3578,13 +3018,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>102</v>
@@ -3595,13 +3035,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920146</v>
+        <v>21330051920149</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
         <v>103</v>
@@ -3612,13 +3052,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920149</v>
+        <v>21330051920150</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
         <v>104</v>
@@ -3629,13 +3069,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920150</v>
+        <v>21330051920382</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
         <v>105</v>
@@ -3649,10 +3089,10 @@
         <v>21330051920392</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
         <v>106</v>
@@ -3668,7 +3108,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3700,157 +3140,157 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920144</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>42</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920144</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920136</v>
+        <v>21330051920384</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>42</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920136</v>
+        <v>21330051920384</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920395</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920141</v>
+        <v>21330051920395</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920382</v>
+        <v>21330051920147</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -3861,25 +3301,117 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920382</v>
+        <v>21330051920147</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>43</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920136</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920382</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
